--- a/docs/templates/initial-stock-survey.xlsx
+++ b/docs/templates/initial-stock-survey.xlsx
@@ -458,6 +458,39 @@
   </x:si>
   <x:si>
     <x:t>so stock does not get doubled. Edit the file and it can be used again.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Photos (optional, step 3)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Product photos are not part of this sheet. They are imported from a FOLDER:</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">   3) press 'Import Photos' and pick the folder of pictures</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name each picture after the product's barcode, the same value you wrote in</x:t>
+  </x:si>
+  <x:si>
+    <x:t>the barcode column:</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">     8801234567890.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A product with no barcode can use its product_name instead.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Use JPG. A photo taken on an iPhone is HEIC by default and cannot be read -</x:t>
+  </x:si>
+  <x:si>
+    <x:t>set the camera to Most Compatible, or convert the folder to JPG first.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>This step can be repeated as often as you like; photos replace, they do not</x:t>
+  </x:si>
+  <x:si>
+    <x:t>pile up. You can also skip it now and add photos months later.</x:t>
   </x:si>
   <x:si>
     <x:t>dosage_form - allowed values</x:t>
@@ -1203,7 +1236,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:A56"/>
+  <x:dimension ref="A1:A72"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="92.710625" style="0" customWidth="1"/>
@@ -1421,57 +1454,132 @@
     </x:row>
     <x:row r="46" spans="1:1">
       <x:c r="A46" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:1">
       <x:c r="A47" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:1">
       <x:c r="A48" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:1">
       <x:c r="A49" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:1">
       <x:c r="A50" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:1">
       <x:c r="A51" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:1">
       <x:c r="A52" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:1">
       <x:c r="A53" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:1">
       <x:c r="A54" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:1">
       <x:c r="A55" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:1">
       <x:c r="A56" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:1">
+      <x:c r="A57" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:1">
+      <x:c r="A58" s="4" t="s">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:1">
+      <x:c r="A60" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:1">
+      <x:c r="A61" s="0" t="s">
         <x:v>62</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:1">
+      <x:c r="A62" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:1">
+      <x:c r="A63" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:1">
+      <x:c r="A64" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:1">
+      <x:c r="A65" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:1">
+      <x:c r="A66" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:1">
+      <x:c r="A67" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:1">
+      <x:c r="A68" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:1">
+      <x:c r="A69" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:1">
+      <x:c r="A70" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:1">
+      <x:c r="A71" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:1">
+      <x:c r="A72" s="0" t="s">
+        <x:v>73</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1499,16 +1607,16 @@
   <x:sheetData>
     <x:row r="1" spans="1:4" s="5" customFormat="1">
       <x:c r="A1" s="5" t="s">
-        <x:v>63</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B1" s="5" t="s">
-        <x:v>64</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C1" s="5" t="s">
-        <x:v>65</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D1" s="5" t="s">
-        <x:v>66</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4">
@@ -1516,13 +1624,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
@@ -1530,13 +1638,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
@@ -1544,13 +1652,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
@@ -1558,13 +1666,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
@@ -1572,13 +1680,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
@@ -1586,13 +1694,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
@@ -1600,13 +1708,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
@@ -1614,13 +1722,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
@@ -1628,13 +1736,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
@@ -1642,13 +1750,13 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
@@ -1656,13 +1764,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
@@ -1670,13 +1778,13 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:4">
@@ -1684,13 +1792,13 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
@@ -1698,13 +1806,13 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
@@ -1712,13 +1820,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
@@ -1726,13 +1834,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
@@ -1740,13 +1848,13 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
@@ -1754,13 +1862,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
@@ -1768,13 +1876,13 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
